--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1173,6 +1173,492 @@
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-001</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>连接建立</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>NapCat 正向 WS 可用</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>start()</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>状态机 disconnected→connecting→connected；生命周期事件不报错</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-002</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>私聊消息归一化</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>已连接</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>收到 private message 包</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>事件 {type:message, subType:private, userId, text, senderName} 各字段正确</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-003</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>群消息归一化</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>已连接</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>收到 group message 包</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>groupId/群名片正确；表情等非文本段原样保留在 segments</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-004</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>API 调用成功</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>已连接</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>callApi(send_private_msg)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>resolve 为响应 data 字段（如 message_id）</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-005</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>API 调用失败</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>已连接</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>服务端回 status=failed retcode=1403</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>reject 带 EBOT-API-1403 与错误文案</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-API-1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-006</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>API 超时</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>服务器收到请求但不回包</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>callApi（超时阈值 80ms）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>reject EBOT-API-TIMEOUT</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-API-TIMEOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-007</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>未连接时调用 API</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>客户端从未 start()</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>callApi</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>立即 reject EBOT-NOT-CONNECTED，不傻等</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-NOT-CONNECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-008</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>断线自动重连</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>连接被服务端主动断开</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>等待重连</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>状态经 reconnecting 回到 connected；退避间隔非降且不低于基数</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-009</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>断线时在途调用</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>有 API 在途未回包时断线</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>服务端掐断连接</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>在途调用立即 reject EBOT-NOT-CONNECTED</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-NOT-CONNECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-010</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>dispose 终态</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>任意运行状态</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>dispose()</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>状态=disposed；不再重连；新调用 reject EBOT-DISPOSED</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-DISPOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-011</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>脏数据容错</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>连接收到非 JSON 包</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>继续收发消息</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>坏包被忽略记日志；连接不崩；后续正常事件照常处理</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-012</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>处理器异常隔离</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>某个事件处理器抛异常</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>继续分发事件</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>其他处理器照常收到事件；连接不断</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-013</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>access_token 传递</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>配置 onebot.token</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>建立连接</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>NapCat 侧收到的 URL 带 access_token=&lt;token&gt;</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TC-OB-014</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>OneBot</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>回复消息构造契约</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>buildMessage(文本/对象/数组/数字)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>CQ 段输出符合契约；非法输入抛 EBOT-BAD-MESSAGE</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-BAD-MESSAGE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1659,6 +1659,921 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-001</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>补全成功</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>模型服务正常</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete(messages)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>返回 content 文本与 usage</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-002</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>reasoning 模型兼容</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>content 为空、reasoning_content 有值</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>退回 reasoning_content 作为回复</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-003</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>4xx 不重试</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>服务端回 401 带 error.message</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>一次请求后 reject EBOT-LLM-HTTP-401，文案透出服务端信息</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-HTTP-401</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-004</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>5xx 重试</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>服务端一直回 503</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>共 3 次尝试后 reject EBOT-LLM-HTTP-5XX</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-HTTP-5XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-005</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>超时</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>服务端响应超过 timeoutMs</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>reject EBOT-LLM-TIMEOUT</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-TIMEOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-006</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>网络不可达</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>地址无可监听端口</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>reject EBOT-LLM-NETWORK</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-NETWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-007</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>空响应</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>content 与 reasoning 均为空</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>reject EBOT-LLM-EMPTY</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-EMPTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TC-LLM-008</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>请求途中 abort signal 触发</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>chatComplete</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>reject EBOT-LLM-CANCELLED</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-CANCELLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-001</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>私聊回复闭环</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>owner.qq=0，模型可用</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>私聊发「你好」</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>模型收到含人设的系统提示词；回复送达本人；会话历史记录一问一答</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-002</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>第二轮携带历史</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>已聊过一轮</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>再发一条消息</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>模型请求包含上一轮 user/assistant 历史</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-003</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>主人模式权限</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>owner.qq=123</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>999 与 123 各发一条</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>只有 123 的消息进模型并收到回复</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-004</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>群聊触发条件</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>groups=[999]，self_id=111</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>非白名单群 / 未@ / @鱼 / 提关键词</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>只有白名单群内 @鱼 或提「大肥鱼/鱼鱼」才回复</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-005</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>命令分流</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>已连接</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>/帮助 /状态 /清空 /未知命令</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>按命令回复对应文案；命令不进模型、不产生会话</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-006</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>并发忙提示</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>上一条回复生成中</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>同一人再发一条</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>立即回「忙」软文案，不并发进模型；第一条完成后正常送达</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-007</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>模型失败软兜底</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>模型抛 LlmError</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>发送消息</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>用户收到鱼鱼的软文案，不暴露错误码/堆栈</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-008</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>超长回复分段</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>模型回复 9000 字</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>发送消息</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>分多条发出，每段 &lt;=4000 字，拼接无损</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-009</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>无文本消息</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>收到纯表情/图片消息</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>发送消息</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>不进模型、不回复（留待表情/语音模块处理）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-010</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>媒体 hook 随回复</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>hooks.sticker 返回图片</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>发送消息</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>回复为 CQ 段数组，含 image 段与文本段</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TC-CHAT-011</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>记忆接口契约</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>注册 memory 接口</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>发送消息</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>回复前调用 retrieve（文本）并注入系统提示词；回复后调用 remember（问答对）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TC-SESS-001</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>会话</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>窗口按轮数裁剪</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>shortTermTurns=2</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>连聊 4 轮</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>历史只保留最近 2 轮（4 条），内容正确</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TC-SESS-002</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>会话</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>多会话隔离</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>多个私聊/群聊对象</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>各自发消息</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>各会话历史互不串味</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TC-SESS-003</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>会话</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>容量淘汰与清空</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>maxPeers=2</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>三个对象各发一条后 clear 一个</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>最老的会话被淘汰；clear 后该会话为空</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TC-SESS-004</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>会话</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>超长与空白消息</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>单条 9000 字 / 纯空白</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>push 消息</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>截断到 4000 字；纯空白不入库</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TC-PER-001</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>人设</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>默认人设</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>未配置 persona.prompt</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>buildSystemPrompt</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>包含「大肥鱼」「鱼鱼」与当天日期</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TC-PER-002</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>人设</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>自定义人设替换</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>配置 persona.prompt</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>buildSystemPrompt</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>整体替换默认人设，不混入默认内容</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TC-PER-003</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>人设</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>长期记忆注入</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>传入 memoryText</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>buildSystemPrompt</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>记忆文本出现在系统提示词，带「不要逐条复述」引导</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TC-PER-004</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>人设</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>自定义名字注入</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>name=肥仔</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>buildSystemPrompt</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>名字被注入提示词</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>连接被服务端主动断开</t>
+          <t>连接被服务端反复断开</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>状态经 reconnecting 回到 connected；退避间隔非降且不低于基数</t>
+          <t>状态经 reconnecting 回到 connected；重连后能再次建立连接（不校验墙钟间隔）</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-OB-009</t>
+          <t>TC-OB-015</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1462,34 +1462,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>断线时在途调用</t>
+          <t>指数退避计算</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>有 API 在途未回包时断线</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>服务端掐断连接</t>
+          <t>reconnectDelay(retry, base, max, jitter)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>在途调用立即 reject EBOT-NOT-CONNECTED</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>EBOT-NOT-CONNECTED</t>
-        </is>
-      </c>
+          <t>延迟按 base*2^retry 增长并封顶 max；非法参数兜底；抖动有界</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-OB-010</t>
+          <t>TC-OB-009</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1499,34 +1495,34 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>dispose 终态</t>
+          <t>断线时在途调用</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>任意运行状态</t>
+          <t>有 API 在途未回包时断线</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>dispose()</t>
+          <t>服务端掐断连接</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>状态=disposed；不再重连；新调用 reject EBOT-DISPOSED</t>
+          <t>在途调用立即 reject EBOT-NOT-CONNECTED</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>EBOT-DISPOSED</t>
+          <t>EBOT-NOT-CONNECTED</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-OB-011</t>
+          <t>TC-OB-010</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1536,30 +1532,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>脏数据容错</t>
+          <t>dispose 终态</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>连接收到非 JSON 包</t>
+          <t>任意运行状态</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>继续收发消息</t>
+          <t>dispose()</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>坏包被忽略记日志；连接不崩；后续正常事件照常处理</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>状态=disposed；不再重连；新调用 reject EBOT-DISPOSED</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-DISPOSED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-OB-012</t>
+          <t>TC-OB-011</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1569,22 +1569,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>处理器异常隔离</t>
+          <t>脏数据容错</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>某个事件处理器抛异常</t>
+          <t>连接收到非 JSON 包</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>继续分发事件</t>
+          <t>继续收发消息</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>其他处理器照常收到事件；连接不断</t>
+          <t>坏包被忽略记日志；连接不崩；后续正常事件照常处理</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-OB-013</t>
+          <t>TC-OB-012</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>access_token 传递</t>
+          <t>处理器异常隔离</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>配置 onebot.token</t>
+          <t>某个事件处理器抛异常</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>建立连接</t>
+          <t>继续分发事件</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>NapCat 侧收到的 URL 带 access_token=&lt;token&gt;</t>
+          <t>其他处理器照常收到事件；连接不断</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-OB-014</t>
+          <t>TC-OB-013</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1635,67 +1635,67 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>回复消息构造契约</t>
+          <t>access_token 传递</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>配置 onebot.token</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>buildMessage(文本/对象/数组/数字)</t>
+          <t>建立连接</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>CQ 段输出符合契约；非法输入抛 EBOT-BAD-MESSAGE</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>EBOT-BAD-MESSAGE</t>
-        </is>
-      </c>
+          <t>NapCat 侧收到的 URL 带 access_token=&lt;token&gt;</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-001</t>
+          <t>TC-OB-014</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>OneBot</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>补全成功</t>
+          <t>回复消息构造契约</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>模型服务正常</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>chatComplete(messages)</t>
+          <t>buildMessage(文本/对象/数组/数字)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>返回 content 文本与 usage</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>CQ 段输出符合契约；非法输入抛 EBOT-BAD-MESSAGE</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-BAD-MESSAGE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-002</t>
+          <t>TC-LLM-001</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1705,22 +1705,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>reasoning 模型兼容</t>
+          <t>补全成功</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>content 为空、reasoning_content 有值</t>
+          <t>模型服务正常</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>chatComplete</t>
+          <t>chatComplete(messages)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>退回 reasoning_content 作为回复</t>
+          <t>返回 content 文本与 usage</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-003</t>
+          <t>TC-LLM-002</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>4xx 不重试</t>
+          <t>reasoning 模型兼容</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>服务端回 401 带 error.message</t>
+          <t>content 为空、reasoning_content 有值</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1753,19 +1753,15 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>一次请求后 reject EBOT-LLM-HTTP-401，文案透出服务端信息</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>EBOT-LLM-HTTP-401</t>
-        </is>
-      </c>
+          <t>退回 reasoning_content 作为回复</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-004</t>
+          <t>TC-LLM-003</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1775,12 +1771,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5xx 重试</t>
+          <t>4xx 不重试</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>服务端一直回 503</t>
+          <t>服务端回 401 带 error.message</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1790,19 +1786,19 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>共 3 次尝试后 reject EBOT-LLM-HTTP-5XX</t>
+          <t>一次请求后 reject EBOT-LLM-HTTP-401，文案透出服务端信息</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>EBOT-LLM-HTTP-5XX</t>
+          <t>EBOT-LLM-HTTP-401</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-005</t>
+          <t>TC-LLM-004</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1812,12 +1808,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>超时</t>
+          <t>5xx 重试</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>服务端响应超过 timeoutMs</t>
+          <t>服务端一直回 503</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1827,19 +1823,19 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>reject EBOT-LLM-TIMEOUT</t>
+          <t>共 3 次尝试后 reject EBOT-LLM-HTTP-5XX</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>EBOT-LLM-TIMEOUT</t>
+          <t>EBOT-LLM-HTTP-5XX</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-006</t>
+          <t>TC-LLM-005</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1849,12 +1845,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>网络不可达</t>
+          <t>超时</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>地址无可监听端口</t>
+          <t>服务端响应超过 timeoutMs</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1864,19 +1860,19 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>reject EBOT-LLM-NETWORK</t>
+          <t>reject EBOT-LLM-TIMEOUT</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>EBOT-LLM-NETWORK</t>
+          <t>EBOT-LLM-TIMEOUT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-007</t>
+          <t>TC-LLM-006</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1886,12 +1882,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>空响应</t>
+          <t>网络不可达</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>content 与 reasoning 均为空</t>
+          <t>地址无可监听端口</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1901,19 +1897,19 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>reject EBOT-LLM-EMPTY</t>
+          <t>reject EBOT-LLM-NETWORK</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>EBOT-LLM-EMPTY</t>
+          <t>EBOT-LLM-NETWORK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-LLM-008</t>
+          <t>TC-LLM-007</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1923,12 +1919,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>空响应</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>请求途中 abort signal 触发</t>
+          <t>content 与 reasoning 均为空</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1938,52 +1934,56 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>reject EBOT-LLM-CANCELLED</t>
+          <t>reject EBOT-LLM-EMPTY</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>EBOT-LLM-CANCELLED</t>
+          <t>EBOT-LLM-EMPTY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-001</t>
+          <t>TC-LLM-008</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聊天</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>私聊回复闭环</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>owner.qq=0，模型可用</t>
+          <t>请求途中 abort signal 触发</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>私聊发「你好」</t>
+          <t>chatComplete</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>模型收到含人设的系统提示词；回复送达本人；会话历史记录一问一答</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t>reject EBOT-LLM-CANCELLED</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-LLM-CANCELLED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-002</t>
+          <t>TC-CHAT-001</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>第二轮携带历史</t>
+          <t>私聊回复闭环</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>已聊过一轮</t>
+          <t>owner.qq=0，模型可用</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>再发一条消息</t>
+          <t>私聊发「你好」</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>模型请求包含上一轮 user/assistant 历史</t>
+          <t>模型收到含人设的系统提示词；回复送达本人；会话历史记录一问一答</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-003</t>
+          <t>TC-CHAT-002</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>主人模式权限</t>
+          <t>第二轮携带历史</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>owner.qq=123</t>
+          <t>已聊过一轮</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>999 与 123 各发一条</t>
+          <t>再发一条消息</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>只有 123 的消息进模型并收到回复</t>
+          <t>模型请求包含上一轮 user/assistant 历史</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2049,7 +2049,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-004</t>
+          <t>TC-CHAT-003</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>群聊触发条件</t>
+          <t>主人模式权限</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>groups=[999]，self_id=111</t>
+          <t>owner.qq=123</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>非白名单群 / 未@ / @鱼 / 提关键词</t>
+          <t>999 与 123 各发一条</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>只有白名单群内 @鱼 或提「大肥鱼/鱼鱼」才回复</t>
+          <t>只有 123 的消息进模型并收到回复</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-005</t>
+          <t>TC-CHAT-004</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>命令分流</t>
+          <t>群聊触发条件</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>已连接</t>
+          <t>groups=[999]，self_id=111</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>/帮助 /状态 /清空 /未知命令</t>
+          <t>非白名单群 / 未@ / @鱼 / 提关键词</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>按命令回复对应文案；命令不进模型、不产生会话</t>
+          <t>只有白名单群内 @鱼 或提「大肥鱼/鱼鱼」才回复</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2115,7 +2115,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-006</t>
+          <t>TC-CHAT-005</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2125,22 +2125,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>并发忙提示</t>
+          <t>命令分流</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>上一条回复生成中</t>
+          <t>已连接</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>同一人再发一条</t>
+          <t>/帮助 /状态 /清空 /未知命令</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>立即回「忙」软文案，不并发进模型；第一条完成后正常送达</t>
+          <t>按命令回复对应文案；命令不进模型、不产生会话</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-007</t>
+          <t>TC-CHAT-006</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2158,22 +2158,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>模型失败软兜底</t>
+          <t>并发忙提示</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>模型抛 LlmError</t>
+          <t>上一条回复生成中</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>发送消息</t>
+          <t>同一人再发一条</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>用户收到鱼鱼的软文案，不暴露错误码/堆栈</t>
+          <t>立即回「忙」软文案，不并发进模型；第一条完成后正常送达</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-008</t>
+          <t>TC-CHAT-007</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>超长回复分段</t>
+          <t>模型失败软兜底</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>模型回复 9000 字</t>
+          <t>模型抛 LlmError</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>分多条发出，每段 &lt;=4000 字，拼接无损</t>
+          <t>用户收到鱼鱼的软文案，不暴露错误码/堆栈</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-009</t>
+          <t>TC-CHAT-008</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>无文本消息</t>
+          <t>超长回复分段</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>收到纯表情/图片消息</t>
+          <t>模型回复 9000 字</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>不进模型、不回复（留待表情/语音模块处理）</t>
+          <t>分多条发出，每段 &lt;=4000 字，拼接无损</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-010</t>
+          <t>TC-CHAT-009</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>媒体 hook 随回复</t>
+          <t>无文本消息</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>hooks.sticker 返回图片</t>
+          <t>收到纯表情/图片消息</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>回复为 CQ 段数组，含 image 段与文本段</t>
+          <t>不进模型、不回复（留待表情/语音模块处理）</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TC-CHAT-011</t>
+          <t>TC-CHAT-010</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>记忆接口契约</t>
+          <t>媒体 hook 随回复</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>注册 memory 接口</t>
+          <t>hooks.sticker 返回图片</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>回复前调用 retrieve（文本）并注入系统提示词；回复后调用 remember（问答对）</t>
+          <t>回复为 CQ 段数组，含 image 段与文本段</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2313,32 +2313,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-001</t>
+          <t>TC-CHAT-011</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>会话</t>
+          <t>聊天</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>窗口按轮数裁剪</t>
+          <t>记忆接口契约</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>shortTermTurns=2</t>
+          <t>注册 memory 接口</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>连聊 4 轮</t>
+          <t>发送消息</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>历史只保留最近 2 轮（4 条），内容正确</t>
+          <t>回复前调用 retrieve（文本）并注入系统提示词；回复后调用 remember（问答对）</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-002</t>
+          <t>TC-SESS-001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>多会话隔离</t>
+          <t>窗口按轮数裁剪</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>多个私聊/群聊对象</t>
+          <t>shortTermTurns=2</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>各自发消息</t>
+          <t>连聊 4 轮</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>各会话历史互不串味</t>
+          <t>历史只保留最近 2 轮（4 条），内容正确</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2379,7 +2379,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-003</t>
+          <t>TC-SESS-002</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2389,22 +2389,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>容量淘汰与清空</t>
+          <t>多会话隔离</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>maxPeers=2</t>
+          <t>多个私聊/群聊对象</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>三个对象各发一条后 clear 一个</t>
+          <t>各自发消息</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>最老的会话被淘汰；clear 后该会话为空</t>
+          <t>各会话历史互不串味</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-004</t>
+          <t>TC-SESS-003</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2422,22 +2422,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>超长与空白消息</t>
+          <t>容量淘汰与清空</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>单条 9000 字 / 纯空白</t>
+          <t>maxPeers=2</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>push 消息</t>
+          <t>三个对象各发一条后 clear 一个</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>截断到 4000 字；纯空白不入库</t>
+          <t>最老的会话被淘汰；clear 后该会话为空</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2445,32 +2445,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TC-PER-001</t>
+          <t>TC-SESS-004</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>人设</t>
+          <t>会话</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>默认人设</t>
+          <t>超长与空白消息</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>未配置 persona.prompt</t>
+          <t>单条 9000 字 / 纯空白</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>buildSystemPrompt</t>
+          <t>push 消息</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>包含「大肥鱼」「鱼鱼」与当天日期</t>
+          <t>截断到 4000 字；纯空白不入库</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TC-PER-002</t>
+          <t>TC-PER-001</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>自定义人设替换</t>
+          <t>默认人设</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>配置 persona.prompt</t>
+          <t>未配置 persona.prompt</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>整体替换默认人设，不混入默认内容</t>
+          <t>包含「大肥鱼」「鱼鱼」与当天日期</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TC-PER-003</t>
+          <t>TC-PER-002</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>长期记忆注入</t>
+          <t>自定义人设替换</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>传入 memoryText</t>
+          <t>配置 persona.prompt</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>记忆文本出现在系统提示词，带「不要逐条复述」引导</t>
+          <t>整体替换默认人设，不混入默认内容</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2544,35 +2544,732 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>TC-PER-003</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>人设</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>长期记忆注入</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>传入 memoryText</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>buildSystemPrompt</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>记忆文本出现在系统提示词，带「不要逐条复述」引导</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>TC-PER-004</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>人设</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>自定义名字注入</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>name=肥仔</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>buildSystemPrompt</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>名字被注入提示词</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-001</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>记忆存储</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>新增与列表</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>facts.json 不存在</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>store.add(文本)</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>条数+1，内容/kind/时间戳正确</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-002</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>记忆存储</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>同义文本合并</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>已有「主人喜欢喝美式」</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>再 add「主人 喜欢 喝美式」</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>归一化去重，不产生第二条，updatedAt 刷新</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-003</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>记忆存储</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>删除与清空</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>有两条记忆</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>remove(id) / clear()</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>按 id 删除；clear 后条数为 0</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-004</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>记忆存储</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>上限淘汰</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>maxFacts=3</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>连加 5 条</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>只保留最新 3 条（FIFO 淘汰最旧）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-005</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>记忆存储</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>持久化读回</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>写入含 embedding 的记忆后重建实例</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>new MemoryStore(同一文件)</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>条数与 embedding 原样读回</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-006</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>记忆存储</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>损坏文件容错</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>facts.json 内容非法 JSON</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>启动存储</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>静默重建为空，后续写入修复文件</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-007</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>记忆提取</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>标准 JSON 解析</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>模型输出 JSON 数组</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>parseFacts</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>输出 [{text,kind}]，kind 合法</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-008</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>记忆提取</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>围栏/杂字容错</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>输出带 ```json 围栏和解释文字</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>parseFacts</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>仍能解析出数组；未知 kind 归一为 fact；空文本条目丢弃</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-009</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>记忆提取</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>坏输出容错</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>非 JSON / 非数组 / 空串</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>parseFacts</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>返回 []</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-010</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>记忆提取</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>模型异常</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>LLM 调用抛错</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>extractFacts</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>返回 [] 且不抛异常（不炸聊天主流程）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-011</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>记忆检索</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>关键词打分排序</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>多条记忆</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>retrieveKeyword(query, topK)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>按重合度降序取 topK；零命中返回 []</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-012</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>记忆检索</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>余弦相似度</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>若干向量</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>cosine(a,b)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>同向量=1、正交=0、维度不符=0</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-013</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>记忆检索</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>embedding API 契约</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>mock /embeddings 服务</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>embedOnce</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>请求路径/模型名正确，返回 data[0].embedding；5xx 抛 EBOT-EMB-HTTP-&lt;status&gt;</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-EMB-HTTP-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-014</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>记忆检索</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>向量路线过滤</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>embedding 三件套配齐，minScore=0.5</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>retrieveMemory</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>按余弦降序取 topK，低于 minScore 的记忆不返回</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-015</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>记忆检索</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>无 embedding 降级</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>只配 topK</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>retrieveMemory</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>自动走关键词路线，结果正确</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-016</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>记忆引擎</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>检索注入</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>有记忆且 longTerm 开</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>retrieve(query)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>命中返回格式化文本；未命中返回空串；longTerm 关返回空串</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-017</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>记忆引擎</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>提取限流</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>extractEvery=3</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>连发 3 轮 remember</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>前 2 轮不调 LLM，第 3 轮提取并写入存储；autoExtract 关时永不提取</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-018</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>记忆引擎</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>手动记忆</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>/记住 xxx 命令</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>存储新增一条并回复确认文案；空白不记</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-019</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>记忆引擎</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>提取失败不炸</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>提取 LLM 抛错</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>remember</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>不抛异常，聊天主流程不受影响</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TC-MEM-020</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>记忆引擎</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>多会话独立计数</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>两个 peer</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>各发 1 轮 remember（extractEvery=2）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>各自计数，都未触发提取</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3271,6 +3271,529 @@
       </c>
       <c r="G83" s="2" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-001</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>收语音</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>base64 record 解析</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>record 段 file=base64://…</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>resolveRecordBytes</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>返回正确字节；空 base64 报 EBOT-STT-BAD-RECORD</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-STT-BAD-RECORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-002</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>收语音</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>URL 下载语音</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>NapCat 提供 http file 地址</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>resolveRecordBytes</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>下载成功返回字节；404 报 EBOT-STT-HTTP-404；超时报 EBOT-STT-TIMEOUT</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-STT-HTTP-404 / EBOT-STT-TIMEOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-003</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>收语音</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>本地文件来源</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>file:// 前缀或裸路径</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>resolveRecordBytes</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>读文件返回字节；文件不存在报 EBOT-STT-FILE</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-STT-FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-004</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>收语音</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>转写服务调用</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>speechToText 服务可用</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>sttTranscribe(ctx, audio)</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>resolve({audio}) → transcribe → 返回修剪后的文本</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-005</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>收语音</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>转写失败路径</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>结果为空 / 服务缺失</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>sttTranscribe</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>空结果报 EBOT-STT-EMPTY；服务拿不到报 EBOT-STT-UNAVAILABLE；服务抛错原样上抛</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-STT-EMPTY / EBOT-STT-UNAVAILABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-006</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>发语音</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>文本截断</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>合成前处理</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>truncateForTts</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>&lt;=150 字原样；长文本按句号边界截断；无句号硬截</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-007</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>发语音</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Piper 本地合成</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>piper 可执行文件+模型</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ttsPiper</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>stdin 文本、output_file 出 wav，返回 {data, format:wav}</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-008</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>发语音</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Piper 失败路径</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>模型缺失/二进制缺失/非零退出/无输出</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>ttsPiper</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>分别报 EBOT-TTS-PIPER-NO-MODEL / -SPAWN / -FAILED / -OUTPUT</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-TTS-PIPER-*</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-009</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>发语音</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 兼容合成</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>云端 TTS 可用</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ttsOpenai</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>POST /audio/speech 载荷正确，返回字节与格式；400 报 EBOT-TTS-HTTP-400；空响应报 -EMPTY；网络失败报 -NETWORK</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-TTS-HTTP-400 / -EMPTY / -NETWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-010</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>发语音</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>引擎路由</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>provider=off / 文本为空</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>synthText</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>off 报 EBOT-TTS-PROVIDER-OFF；空文本报 EBOT-TTS-EMPTY</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-TTS-PROVIDER-OFF / EBOT-TTS-EMPTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-011</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>语音集成</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>收语音闭环</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>sttEnabled 且转写可用</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>发一条语音消息</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>转写文本作为 user 消息进模型，回复正常送达</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-012</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>语音集成</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>转写失败软兜底</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>转写 hook 抛错/返回 null</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>发语音消息</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>回「没听清」软文案，不进模型、不暴露错误</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-013</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>语音集成</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>回复自动配音</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>voice.mode=on 且 TTS 可用</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>发文字消息</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>回复为 CQ 段数组，含 record 段（base64:// 音频）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-014</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>语音集成</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>smart 模式</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>voice.mode=smart</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>回复 &gt;80 字</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>不配音（返回纯文本）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TC-VOI-015</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>语音命令</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>/语音 命令</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>TTS 各状态</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>/语音（空参/未启用/成功/失败）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>空参给用法提示；未启用给设置引导；成功发 record 段；失败回软文案</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3794,6 +3794,270 @@
       </c>
       <c r="G98" s="2" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-001</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>目录扫描与标签合并</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>目录含子目录/tags.json/非图片</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>scanStickers</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>子目录名、tags.json、文件名词三处标签合并；非图片忽略；不存在返回 []</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-002</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>情绪词匹配</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>内置情绪词表</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>matchEmotion(文本)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>命中返回情绪标签；未命中/空文本返回 null</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-003</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>情绪命中必发</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>rate=0 且库有「开心」图</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>pick(含情绪词文本)×20</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>每次都从情绪池里选到图（不受 rate 影响）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-004</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>随机概率</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>rate=0 / rate=1</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>pick(无情绪词文本)×20</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>rate=0 全部不发；rate=1 全部发</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-005</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>空库行为</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>目录无图片</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>pick/random/search</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>pick 与 random 返回 null；search 返回 []</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-006</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>关键词搜索</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>多样例库</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>search(词)</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>文件名、tags.json 标签均可命中；无命中返回 []</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-007</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>自动重扫</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>库中新增图片</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>5 分钟内/后 search</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>4 分钟不重扫；超过 5 分钟自动发现新图</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TC-STK-008</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>表情包</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>hook 与命令</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>库已就绪 / 未启用</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>回复触发 sticker hook 与 /表情 命令</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>命中情绪随回复带 image 段；未启用不发并提示；/表情 带词命中/空库/未启用各有文案</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4058,6 +4058,336 @@
       </c>
       <c r="G106" s="2" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-001</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>时间窗判断</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>各种时间与窗口（含跨夜）</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>inWindow(now, start, end)</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>窗口内 true、边界含头不含尾；跨夜窗口（22:00-02:00）两端都正确</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-002</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>调度计算</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>固定 rng</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>nextFireAt(now, opts)</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>rng=0 取最小间隔；≈1 取最大；落在窗口外顺延到窗口内；跨夜窗口顺延正确</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-003</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>话题生成</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>记忆事实/空/自定义话题</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>pickTopic</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>有记忆且 rng&lt;0.6 走记忆钩子句式；否则池子随机；用户话题可选中；空池有兜底</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-004</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>引擎闭环</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>全部条件满足</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>start() 后等待多次调度</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>到点触发发送话题并重新调度（多次）</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-005</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>五道闸</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>enabled=false / 主人未配 / 未连接 / 冷却中</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>触发调度</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>任一闸关闭都不发消息</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-006</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>时间窗外拦截</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>注入凌晨 3 点时钟，窗口 09:00-23:00</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>触发调度</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>不发消息</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-007</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>记忆驱动</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>recentFacts 有事实且 rng=0</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>触发调度</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>话题内容来自记忆钩子</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-008</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>失败恢复</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>send 抛异常</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>多次触发</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>不崩、继续调度（attempts 增长、fireCount 不增长）</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-009</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>dispose 终态</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>运行中</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>dispose()</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>不再触发新调度</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>TC-PRO-010</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>主动聊天</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>主人活动冷却</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>装配模块监听事件</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>主人/陌生人发消息</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>主人消息刷新冷却起点；陌生人消息不影响</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4388,6 +4388,336 @@
       </c>
       <c r="G116" s="2" t="inlineStr"/>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-001</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>条目查找</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>configEditor 含 bili-scroll 条目</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>findBiliEntry</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>按 id 或 name 找到；缺失/空返回 undefined</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-002</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>配置同步</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>mentionName 有值</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>syncBiliConfig</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>首次 edit 写入 {mentionName, autoComment}；重复调用被变化检测挡住；空昵称不写；edit 抛错返回 ok:false</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-003</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>日报读取</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>报告文件存在/缺失</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>readReport</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>存在返回文本与 mtime；缺失返回 exists:false 不抛错</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-004</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>内容签名</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>两段文本</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>内容变签名变；同内容稳定；空内容空串</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-005</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>摘要解析</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>### BV 块报告</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>extractSummary</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>提取 {bv,title,url}；加粗标题优先，否则块首行；无 BV 返回 []</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-006</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>轮询通知</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>报告出现后 pollNow</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>pollNow×2</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>第一次通知；内容没变第二次不通知（unchanged）</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-007</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>报告追加再通知</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>通知过一轮后报告追加新 BV</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>pollNow</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>再次通知且包含新条目</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-008</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>通知形态</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>reportToQq=summary/full/off</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>pollNow</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>summary 只发摘要；full 含报告正文；off 不通知</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-009</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>开关拦截</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>enabled=false / notifyQq=false</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>pollNow / syncNow</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>不通知、不同步</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>TC-BIL-010</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>B站联动</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>定时器生命周期</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>start 后 dispose</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>start/pollNow/dispose</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>定时器创建；dispose 后置空不再轮询</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4718,6 +4718,303 @@
       </c>
       <c r="G126" s="2" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-001</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>私聊问答闭环</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>真实 apply + mock NapCat/LLM</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>私聊发「你好呀」</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>LLM 收到消息，回复经 NapCat 送达主人</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-002</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>状态命令</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>已连接</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>/状态</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>回复含连接状态与记忆条数</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-003</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>语音消息闭环</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>record 消息</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>发语音</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>转写文本进模型并正常回复</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-004</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>记忆命令闭环</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>无记忆</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>/记住 xx → /状态</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>确认文案；记忆条数变 1</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-005</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>表情包随回复</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>库有图 + 情绪词</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>发「太开心了哈哈」</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>回复为 CQ 段数组且含 image 段</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-006</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>语音回复闭环</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>mode=on + 云端 TTS</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>发文字</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>回复含 record 段（base64 音频）</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-007</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>权限隔离</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>owner.qq=111</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>陌生人 999 发消息</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>不产生任何回复/API 调用</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-008</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>卸载收摊</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>运行中</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>执行 cleanup 链</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>连接关闭，不再重连</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>TC-E2E-009</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>端到端</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>日志落地</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>真实 apply</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>启动</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>插件家目录 logs/app.log 出现「已挂载」</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5015,6 +5015,307 @@
       </c>
       <c r="G135" s="2" t="inlineStr"/>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-001</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>同源检查</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>各 Host/Origin 组合</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>sameOriginOk(host, origin, referer)</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>loopback 无 Origin 放行；同源放行；外部 Origin 与非 loopback Host 拒绝；同机不同端口拒绝</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-002</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>读取配置</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>settings 服务正常</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/ebot-qq/config</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>返回默认值合并后的配置、secret 状态（set 布尔）、revision</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-003</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>保存配置</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>patch 合法</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/ebot-qq/config</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>走 settings.update(ns, patch, revision) 热更新，返回 ok</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-004</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>保存校验失败</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>patch 含非法值（url=ftp://…）</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>回 400 + 逐字段 errors；不写 settings</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>EBOT-CFG-URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-005</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>保存冲突</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>settings.update 抛 SETTINGS_CONFLICT</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>回 409 + conflict 标记，提示刷新重试</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-006</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>服务缺失与坏输入</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>settings 缺失 / patch 非对象</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>GET/POST</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>GET 返回 ok:false；POST 返回 ok:false 不写</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-007</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>信任栅栏</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>connection.requestRejection 拒绝</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>任意请求</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>回拒绝码（401/403），不进业务</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-008</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>路由分发</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>各方法与路径</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>GET/POST/未知路径</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>200/400/409/404 状态码正确</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-009</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>设置面板</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>面板注册</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>client.js 加载</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>settings.plugins.tab 注册（id=ebot-qq, label=大肥鱼）</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>设置 → 插件 分区出现「大肥鱼」标签页，表单可读写配置</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
